--- a/02_加值成品/九下/九下3-1_三種難度測驗卷.xlsx
+++ b/02_加值成品/九下/九下3-1_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三下學期 九下3-1 大氣與天氣要素　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國三下學期 九下3-1 大氣與天氣要素　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>天氣現象主要發生在哪層？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>氣壓低</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>下降</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>對流層</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>最底</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>大氣依什麼變化分層？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>對流層</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>濕度</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>溫度</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>分層</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>空氣重量造成的壓力是？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>氣壓</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>溫度</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>天氣要素</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>大氣壓</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>高處氣壓較？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>溫度</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>天氣要素</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>氣壓低</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>較低</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>氣溫濕度風屬於？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>氣壓</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>濕度</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>氣壓低</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>天氣要素</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>要素</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>空氣中水氣多寡是？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>天氣要素</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>溫度</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>濕度</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>空氣重量</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>水氣</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>大氣最靠近地面的一層是？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>溫度</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>氣壓低</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>對流層</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>空氣重量</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>底層</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>大氣有沒有重量？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>有</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>濕度</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>溫度</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>產氣壓</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>天氣現象主要發生在大氣哪一層？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>對流層</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>空氣重量</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>氣壓</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>天氣要素</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>最底</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>空氣中水氣的多寡稱？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>對流層</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>濕度</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>天氣要素</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>水氣</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三下學期 九下3-1 大氣與天氣要素　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國三下學期 九下3-1 大氣與天氣要素　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>對流層內氣溫隨高度？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>溫度</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>下降</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>需加壓艙維持</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>遞減</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>高山氣壓比平地？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>氣壓</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>下降</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>溫度</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>高處</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>天氣要素包括哪些？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>氣溫氣壓濕度風降水</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>阻擋輻射調節溫度</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>基礎觀測前移,國中重結構</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>水氣集中且有對流運動</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>綜合</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>平流層在對流層的？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>水氣多</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>空氣重量</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>上方</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>上層</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>為何高山煮飯不易熟？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>上方</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>氣壓低沸點降</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>氣壓低</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>氣壓</t>
         </is>
       </c>
-    </row>
-    <row r="8" ht="34" customHeight="1">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>氣壓</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>濕度高代表空氣中？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>水氣多</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>溫度</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>上方</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>對流層</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>潮濕</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>氣壓的成因是？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>空氣重量</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>濕度</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>氣壓低沸點降</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>大氣</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>雲量也是一種？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>天氣要素</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>氣壓</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>下降</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>要素</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>對流層氣溫隨高度上升而？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>天氣要素</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>氣壓</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>對流層</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>下降</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>遞減</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>高山上氣壓比平地？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>溫度</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>天氣要素</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>水氣多</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>高處低</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三下學期 九下3-1 大氣與天氣要素　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國三下學期 九下3-1 大氣與天氣要素　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>為何天氣變化主要發生在對流層？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>基礎觀測前移,國中重結構</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>水氣集中且有對流運動</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>高處氣壓低沸點降空氣稀薄</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>促成對流形成雲雨</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>對流</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>用氣壓解釋高山現象(沸點空氣稀薄)？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>水氣集中且有對流運動</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>基礎觀測前移,國中重結構</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>高處氣壓低沸點降空氣稀薄</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>促成對流形成雲雨</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>氣壓</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>對流層氣溫隨高度下降的影響？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>氣溫氣壓濕度風降水</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>水氣集中且有對流運動</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>由氣溫氣壓濕度風雲降水共同呈現</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>促成對流形成雲雨</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>對流</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>天氣要素如何綜合描述某地天氣？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>促成對流形成雲雨</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>氣溫氣壓濕度風降水</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>高壓流向低壓形成風</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>由氣溫氣壓濕度風雲降水共同呈現</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>綜合</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>為何說大氣像一層保護與調節？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>高處氣壓低沸點降空氣稀薄</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>水氣集中且有對流運動</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>阻擋輻射調節溫度</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>由氣溫氣壓濕度風雲降水共同呈現</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>功能</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>氣壓差如何影響風的形成？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>基礎觀測前移,國中重結構</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>高壓流向低壓形成風</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>阻擋輻射調節溫度</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>促成對流形成雲雨</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>風</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>高空氣壓低對飛行有何考量？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>需加壓艙維持</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>水氣多</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>天氣要素</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>應用</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>為何課綱把氣象觀測移國小？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>高處氣壓低沸點降空氣稀薄</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>由氣溫氣壓濕度風雲降水共同呈現</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>基礎觀測前移,國中重結構</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>阻擋輻射調節溫度</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>課綱</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>為何高山上水的沸點較低？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>氣壓</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>對流層</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>氣壓低沸點降</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>氣壓低</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>氣壓</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>氣壓差如何造成風？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>氣溫氣壓濕度風降水</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>水氣集中且有對流運動</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>促成對流形成雲雨</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>空氣由高壓流向低壓</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>風</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/九下/九下3-1_三種難度測驗卷.xlsx
+++ b/02_加值成品/九下/九下3-1_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>最底</t>
+          <t>最底：大氣最靠近地面的對流層裡有豐富的水氣和上下對流，天氣現象大多在這裡發生</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>分層</t>
+          <t>分層：科學家依照氣溫隨高度變化的情況，把大氣由下而上分成好幾層</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>大氣壓</t>
+          <t>大氣壓：空氣雖然看不見，但也有重量，這些重量壓下來形成的壓力就是氣壓</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>較低</t>
+          <t>較低：越往高處空氣越稀薄、上方壓下來的空氣也越少，所以氣壓會比較低</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>要素</t>
+          <t>要素：氣溫、濕度、風等都是用來描述某地天氣狀況的重要天氣要素</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>水氣</t>
+          <t>水氣：濕度就是用來表示空氣中含有多少水氣的一種天氣要素</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>底層</t>
+          <t>底層：對流層是大氣中最靠近地面的一層，也是我們日常生活感受天氣變化的地方</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>產氣壓</t>
+          <t>產氣壓：大氣雖然是氣體，但確實有重量，正因為有重量才會產生氣壓</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>最底</t>
+          <t>最底：對流層最靠近地面又集中水氣，天氣現象大多在這一層發生</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>水氣</t>
+          <t>水氣：濕度就是用來表示空氣中含有多少水氣的一種天氣要素</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>遞減</t>
+          <t>遞減：在對流層裡，海拔越高氣溫通常越低，這是它的重要特性之一</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>高處</t>
+          <t>高處：山越高、空氣越稀薄，上方壓下來的空氣重量變少，所以氣壓比平地低</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>綜合</t>
+          <t>綜合：氣溫、氣壓、濕度、風和降水等，都是組成天氣描述的重要要素</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>上層</t>
+          <t>上層：大氣分層由下而上，平流層是位在對流層上方的下一層</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>氣壓</t>
+          <t>氣壓：高山上氣壓較低，水的沸點會跟著下降，水還沒到平地的100度就沸騰了，所以食物不易煮熟</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>潮濕</t>
+          <t>潮濕：濕度數值越高，代表空氣裡含有的水氣量越多，感覺也比較潮濕</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>大氣</t>
+          <t>大氣：氣壓是由於空氣本身有重量，向下壓在物體表面所形成的壓力</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>要素</t>
+          <t>要素：天空中雲的多寡(雲量)也是用來描述天氣狀況的一項重要要素</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>遞減</t>
+          <t>遞減：在對流層裡，海拔越高氣溫通常隨之下降</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>高處低</t>
+          <t>高處低：山越高空氣越稀薄，上方壓下來的空氣重量變少，氣壓比平地低</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>對流</t>
+          <t>對流：對流層裡集中了大氣中大部分的水氣，加上空氣不斷上升下降形成對流運動，因此天氣變化主要發生在這一層</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>氣壓</t>
+          <t>氣壓：高山地區氣壓較低，會使水的沸點下降，同時空氣分子也比平地稀薄，這就是登山時常見的現象成因</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>對流</t>
+          <t>對流：對流層裡氣溫隨高度上升而降低，使暖空氣不斷上升、冷空氣下降，形成對流運動，進而促成雲雨的產生</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>綜合</t>
+          <t>綜合：要完整描述某地的天氣狀況，需要同時參考氣溫、氣壓、濕度、風、雲量和降水等多項要素一起判斷</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>功能</t>
+          <t>功能：大氣層能阻擋部分太陽輻射與宇宙射線，也能保留地表熱量，讓地球溫度維持在適合生物生存的範圍</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>風</t>
+          <t>風：空氣會從氣壓較高的地方流向氣壓較低的地方，這股流動的空氣就形成了風</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>應用</t>
+          <t>應用：高空的氣壓比地面低很多，飛機必須設計加壓艙，維持艙內接近地面的氣壓，乘客才能正常呼吸</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>課綱</t>
+          <t>課綱：簡單的氣象觀測活動安排在國小階段學習，國中課程則把重點放在大氣的分層結構與天氣要素的理解</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>氣壓</t>
+          <t>氣壓：高山上氣壓比平地低，使水不需加熱到100度就能沸騰，所以沸點較低</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>風</t>
+          <t>風：空氣會從氣壓較高的地方流向氣壓較低的地方，這股流動的空氣就形成風</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/九下/九下3-1_三種難度測驗卷.xlsx
+++ b/02_加值成品/九下/九下3-1_三種難度測驗卷.xlsx
@@ -648,12 +648,12 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>溫度</t>
+          <t>下降</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>有</t>
+          <t>空氣重量</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -688,17 +688,17 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>空氣重量</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>天氣要素</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
           <t>溫度</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>天氣要素</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>氣壓低</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
@@ -1084,17 +1084,17 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>氣壓</t>
+          <t>對流層</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>下降</t>
+          <t>濕度</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>溫度</t>
+          <t>空氣重量</t>
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>上方</t>
+          <t>溫度</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -1209,12 +1209,12 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>氣壓低</t>
+          <t>濕度</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>氣壓</t>
+          <t>需加壓艙維持</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -1409,12 +1409,12 @@
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>天氣要素</t>
+          <t>下降</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>水氣多</t>
+          <t>有</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
@@ -1835,17 +1835,17 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>氣壓</t>
+          <t>有</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>對流層</t>
+          <t>天氣要素</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>氣壓低沸點降</t>
+          <t>濕度</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
